--- a/src/nodes/HPC/compressor_stage_3_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_3_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00059143420473660262</v>
       </c>
       <c r="B2">
-        <v>0.00046793596783364574</v>
+        <v>0.00051170209898415426</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0011828684094732052</v>
       </c>
       <c r="B3">
-        <v>0.00078499973811826072</v>
+        <v>0.00084532602700139415</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.001774302614209808</v>
       </c>
       <c r="B4">
-        <v>0.0010686683479031206</v>
+        <v>0.0011417696156085647</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0023657368189464105</v>
       </c>
       <c r="B5">
-        <v>0.001325786305972469</v>
+        <v>0.00140917852884033</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0029571710236830128</v>
       </c>
       <c r="B6">
-        <v>0.0015593130738342786</v>
+        <v>0.0016510423197733063</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0035486052284196159</v>
       </c>
       <c r="B7">
-        <v>0.0017710343227032546</v>
+        <v>0.0018694489743714252</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0041400394331562182</v>
       </c>
       <c r="B8">
-        <v>0.0019620954658525515</v>
+        <v>0.0020657214084160158</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.004731473637892821</v>
       </c>
       <c r="B9">
-        <v>0.0021341101233515116</v>
+        <v>0.0022417511486135734</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0053229078426294228</v>
       </c>
       <c r="B10">
-        <v>0.0022887875510264541</v>
+        <v>0.0023995475687278636</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0059143420473660255</v>
       </c>
       <c r="B11">
-        <v>0.0024277513409354272</v>
+        <v>0.0025410228198265812</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0065057762521026283</v>
       </c>
       <c r="B12">
-        <v>0.002551938366283828</v>
+        <v>0.0026672676154474279</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0070972104568392319</v>
       </c>
       <c r="B13">
-        <v>0.0026596242886347226</v>
+        <v>0.0027761841417042123</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0076886446615758337</v>
       </c>
       <c r="B14">
-        <v>0.0027498225278813791</v>
+        <v>0.0028665623172430777</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0082800788663124365</v>
       </c>
       <c r="B15">
-        <v>0.0028271587488802072</v>
+        <v>0.0029439315182634021</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.00887151307104904</v>
       </c>
       <c r="B16">
-        <v>0.00289587458999234</v>
+        <v>0.003013362262913221</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.0094629472757856419</v>
       </c>
       <c r="B17">
-        <v>0.0029530633386346604</v>
+        <v>0.0030713501795819813</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.010054381480522245</v>
       </c>
       <c r="B18">
-        <v>0.0029949362457193812</v>
+        <v>0.0031133348381281252</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.010645815685258846</v>
       </c>
       <c r="B19">
-        <v>0.0030213247670842786</v>
+        <v>0.003139106464044679</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.01123724988999545</v>
       </c>
       <c r="B20">
-        <v>0.003032965409798521</v>
+        <v>0.0031495429467333115</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.011828684094732051</v>
       </c>
       <c r="B21">
-        <v>0.0030305946809312764</v>
+        <v>0.0031455221755956929</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.012420118299468654</v>
       </c>
       <c r="B22">
-        <v>0.0030148136358385132</v>
+        <v>0.003127761430190799</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.013011552504205257</v>
       </c>
       <c r="B23">
-        <v>0.002985681523023405</v>
+        <v>0.0030963355507068265</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.013602986708941861</v>
       </c>
       <c r="B24">
-        <v>0.0029431221392759274</v>
+        <v>0.0030511587674892779</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.014194420913678464</v>
       </c>
       <c r="B25">
-        <v>0.0028870592813860555</v>
+        <v>0.0029921453108836555</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.014785855118415063</v>
       </c>
       <c r="B26">
-        <v>0.0028173863570560903</v>
+        <v>0.0029191748895004812</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.015377289323151668</v>
       </c>
       <c r="B27">
-        <v>0.0027338752176376364</v>
+        <v>0.0028319891250103554</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.015968723527888268</v>
       </c>
       <c r="B28">
-        <v>0.0026362673253946252</v>
+        <v>0.0027302951173488977</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.016560157732624873</v>
       </c>
       <c r="B29">
-        <v>0.002524304142590987</v>
+        <v>0.0026137999664517294</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.017151591937361477</v>
       </c>
       <c r="B30">
-        <v>0.00239780986184522</v>
+        <v>0.0024823122732523253</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.017743026142098078</v>
       </c>
       <c r="B31">
-        <v>0.00225693959719409</v>
+        <v>0.0023360466426755773</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.018334460346834679</v>
       </c>
       <c r="B32">
-        <v>0.0021019311930289279</v>
+        <v>0.0021753191806442329</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.018925894551571284</v>
       </c>
       <c r="B33">
-        <v>0.0019330224937410667</v>
+        <v>0.0020004459930810397</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.019517328756307885</v>
       </c>
       <c r="B34">
-        <v>0.0017502853046367629</v>
+        <v>0.0018115468579994003</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.020108762961044489</v>
       </c>
       <c r="B35">
-        <v>0.0015531272746819719</v>
+        <v>0.0016079562417753428</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.02070019716578109</v>
       </c>
       <c r="B36">
-        <v>0.0013407900137575749</v>
+        <v>0.0013888122828755517</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.021291631370517691</v>
       </c>
       <c r="B37">
-        <v>0.00111251513174445</v>
+        <v>0.0011532531197667073</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.021883065575254296</v>
       </c>
       <c r="B38">
-        <v>0.00086715561992313007</v>
+        <v>0.00089995396600026827</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.0224744997799909</v>
       </c>
       <c r="B39">
-        <v>0.00060200999517275478</v>
+        <v>0.00062573833546678719</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.0230659339847275</v>
       </c>
       <c r="B40">
-        <v>0.00031398815577211544</v>
+        <v>0.00032696681714159022</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.023657368189464102</v>
       </c>
       <c r="B41">
-        <v>5.25299097319556E-18</v>
+        <v>5.33506895715174E-18</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.0230659339847275</v>
       </c>
       <c r="B43">
-        <v>0.00018420154207736796</v>
+        <v>0.00017122288070789323</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.0224744997799909</v>
       </c>
       <c r="B44">
-        <v>0.00036472659223243026</v>
+        <v>0.00034099825193839784</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.021883065575254296</v>
       </c>
       <c r="B45">
-        <v>0.00053917215915174808</v>
+        <v>0.00050637381307460988</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.021291631370517691</v>
       </c>
       <c r="B46">
-        <v>0.00070513525152187827</v>
+        <v>0.000664397263499621</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.02070019716578109</v>
       </c>
       <c r="B47">
-        <v>0.00086056732257781007</v>
+        <v>0.00081254505345983348</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.020108762961044489</v>
       </c>
       <c r="B48">
-        <v>0.0010048376037482625</v>
+        <v>0.00095000863665489126</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.019517328756307885</v>
       </c>
       <c r="B49">
-        <v>0.0011376697710103886</v>
+        <v>0.001076408217647751</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.018925894551571284</v>
       </c>
       <c r="B50">
-        <v>0.00125878750034134</v>
+        <v>0.0011913640010013671</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.018334460346834679</v>
       </c>
       <c r="B51">
-        <v>0.0013680513168758796</v>
+        <v>0.0012946633292605747</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.017743026142098078</v>
       </c>
       <c r="B52">
-        <v>0.0014658691423792166</v>
+        <v>0.0013867620968977291</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.017151591937361477</v>
       </c>
       <c r="B53">
-        <v>0.00155278574777417</v>
+        <v>0.001468283336367065</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.016560157732624873</v>
       </c>
       <c r="B54">
-        <v>0.0016293459039835602</v>
+        <v>0.0015398500801228176</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.015968723527888268</v>
       </c>
       <c r="B55">
-        <v>0.0016959894058518976</v>
+        <v>0.0016019616138976249</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.015377289323151668</v>
       </c>
       <c r="B56">
-        <v>0.0017527361439104523</v>
+        <v>0.001654622236537734</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.014785855118415063</v>
       </c>
       <c r="B57">
-        <v>0.001799501032612186</v>
+        <v>0.0016977125001677962</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.014194420913678464</v>
       </c>
       <c r="B58">
-        <v>0.0018361989864100602</v>
+        <v>0.0017311129569124609</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.013602986708941861</v>
       </c>
       <c r="B59">
-        <v>0.001862755857142425</v>
+        <v>0.001754719228929075</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.013011552504205257</v>
       </c>
       <c r="B60">
-        <v>0.0018791412461891897</v>
+        <v>0.0017684872185057686</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.012420118299468654</v>
       </c>
       <c r="B61">
-        <v>0.0018853356923156518</v>
+        <v>0.0017723878979633663</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.011828684094732051</v>
       </c>
       <c r="B62">
-        <v>0.00188131973428711</v>
+        <v>0.0017663922396226937</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.01123724988999545</v>
       </c>
       <c r="B63">
-        <v>0.0018671900404506213</v>
+        <v>0.0017506125035158314</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.010645815685258846</v>
       </c>
       <c r="B64">
-        <v>0.0018435077974802803</v>
+        <v>0.0017257261005198805</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.010054381480522245</v>
       </c>
       <c r="B65">
-        <v>0.0018109503216319407</v>
+        <v>0.0016925517292231964</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.0094629472757856419</v>
       </c>
       <c r="B66">
-        <v>0.0017701949291614556</v>
+        <v>0.0016519080882141351</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.00887151307104904</v>
       </c>
       <c r="B67">
-        <v>0.0017209978607835286</v>
+        <v>0.0016035101878626474</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0082800788663124365</v>
       </c>
       <c r="B68">
-        <v>0.001659431055048259</v>
+        <v>0.0015426582856650642</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0076886446615758337</v>
       </c>
       <c r="B69">
-        <v>0.0015824246342643884</v>
+        <v>0.0014656848449026894</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0070972104568392319</v>
       </c>
       <c r="B70">
-        <v>0.0014940257579398261</v>
+        <v>0.0013774659048703365</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0065057762521026283</v>
       </c>
       <c r="B71">
-        <v>0.00139864587464783</v>
+        <v>0.0012833166254842304</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0059143420473660255</v>
       </c>
       <c r="B72">
-        <v>0.0012950365520238857</v>
+        <v>0.0011817650731327318</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0053229078426294228</v>
       </c>
       <c r="B73">
-        <v>0.0011811873740123571</v>
+        <v>0.0010704273563109474</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.004731473637892821</v>
       </c>
       <c r="B74">
-        <v>0.0010576998707308948</v>
+        <v>0.00095005884546883312</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0041400394331562182</v>
       </c>
       <c r="B75">
-        <v>0.00092583604021790787</v>
+        <v>0.00082221009765444343</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0035486052284196159</v>
       </c>
       <c r="B76">
-        <v>0.0007868878060215479</v>
+        <v>0.00068847315435337719</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0029571710236830128</v>
       </c>
       <c r="B77">
-        <v>0.0006420206144440026</v>
+        <v>0.000550291368504975</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0023657368189464105</v>
       </c>
       <c r="B78">
-        <v>0.00049186407729385942</v>
+        <v>0.00040847185442599853</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.001774302614209808</v>
       </c>
       <c r="B79">
-        <v>0.00033765567084867985</v>
+        <v>0.00026455440314323582</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0011828684094732052</v>
       </c>
       <c r="B80">
-        <v>0.00018173684928692629</v>
+        <v>0.00012141056040379286</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00059143420473660262</v>
       </c>
       <c r="B81">
-        <v>3.0274656328559838E-05</v>
+        <v>-1.3491474821948732E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00064109146724713355</v>
       </c>
       <c r="B2">
-        <v>0.00059651793458890764</v>
+        <v>0.00069139947174148332</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0012821829344942671</v>
       </c>
       <c r="B3">
-        <v>0.00097093763799086874</v>
+        <v>0.001101720297309284</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0019232744017414008</v>
       </c>
       <c r="B4">
-        <v>0.0013013477746705762</v>
+        <v>0.0014598255853740675</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0025643658689885342</v>
       </c>
       <c r="B5">
-        <v>0.0015979650300079788</v>
+        <v>0.0017787528237716702</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0032054573362356674</v>
       </c>
       <c r="B6">
-        <v>0.0018651257421389885</v>
+        <v>0.0020639875475522017</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0038465488034828015</v>
       </c>
       <c r="B7">
-        <v>0.002105402915874216</v>
+        <v>0.0023187581561740622</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0044876402707299352</v>
       </c>
       <c r="B8">
-        <v>0.0023204062178235926</v>
+        <v>0.0025450591277528215</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0051287317379770684</v>
       </c>
       <c r="B9">
-        <v>0.0025124730610495459</v>
+        <v>0.0027458303551275024</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0057698232052242017</v>
       </c>
       <c r="B10">
-        <v>0.0026840938069637213</v>
+        <v>0.0029242128318420291</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0064109146724713349</v>
       </c>
       <c r="B11">
-        <v>0.00283764286392214</v>
+        <v>0.0030832065395364821</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.007052006139718469</v>
       </c>
       <c r="B12">
-        <v>0.0029744591056359488</v>
+        <v>0.0032244838656875943</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0076930976069656031</v>
       </c>
       <c r="B13">
-        <v>0.0030918552202924177</v>
+        <v>0.0033445478330225474</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0083341890742127354</v>
       </c>
       <c r="B14">
-        <v>0.00318826951295017</v>
+        <v>0.0034413522134387007</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.00897528054145987</v>
       </c>
       <c r="B15">
-        <v>0.0032706689416771113</v>
+        <v>0.0035238231402636598</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.0096163720087070019</v>
       </c>
       <c r="B16">
-        <v>0.0033454425783026572</v>
+        <v>0.003600146631646488</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.010257463475954137</v>
       </c>
       <c r="B17">
-        <v>0.0034081392966929694</v>
+        <v>0.0036645758835918223</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.01089855494320127</v>
       </c>
       <c r="B18">
-        <v>0.0034529753132081157</v>
+        <v>0.0037096541685040186</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.011539646410448403</v>
       </c>
       <c r="B19">
-        <v>0.0034796764121470254</v>
+        <v>0.0037350178865307327</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.012180737877695537</v>
       </c>
       <c r="B20">
-        <v>0.0034893457697933437</v>
+        <v>0.0037420767197554466</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.01282182934494267</v>
       </c>
       <c r="B21">
-        <v>0.0034830865624307164</v>
+        <v>0.0037322403502616417</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.013462920812189803</v>
       </c>
       <c r="B22">
-        <v>0.0034618011469253916</v>
+        <v>0.0037066630998653046</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.014104012279436938</v>
       </c>
       <c r="B23">
-        <v>0.0034255886024740323</v>
+        <v>0.0036654778493124449</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.014745103746684071</v>
       </c>
       <c r="B24">
-        <v>0.0033743471888559059</v>
+        <v>0.0036085621190815776</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.015386195213931206</v>
       </c>
       <c r="B25">
-        <v>0.0033079751658502774</v>
+        <v>0.0035357934296512184</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.016027286681178338</v>
       </c>
       <c r="B26">
-        <v>0.0032263294592671295</v>
+        <v>0.0034469990082756064</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.016668378148425471</v>
       </c>
       <c r="B27">
-        <v>0.0031291016590393</v>
+        <v>0.0033418049093118744</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.017309469615672604</v>
       </c>
       <c r="B28">
-        <v>0.0030159420211303442</v>
+        <v>0.0032197868938928821</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.017950561082919741</v>
       </c>
       <c r="B29">
-        <v>0.0028865008015038153</v>
+        <v>0.0030805207231514873</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.018591652550166874</v>
       </c>
       <c r="B30">
-        <v>0.0027405593232724375</v>
+        <v>0.002923753918651067</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.019232744017414004</v>
       </c>
       <c r="B31">
-        <v>0.0025784231781456135</v>
+        <v>0.0027499210436770752</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.019873835484661137</v>
       </c>
       <c r="B32">
-        <v>0.0024005290249819134</v>
+        <v>0.0025596284219454807</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.020514926951908274</v>
       </c>
       <c r="B33">
-        <v>0.0022073135226399103</v>
+        <v>0.002353482377172257</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.021156018419155407</v>
       </c>
       <c r="B34">
-        <v>0.0019989687239629051</v>
+        <v>0.0021317789632644439</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.02179710988640254</v>
       </c>
       <c r="B35">
-        <v>0.0017747082577331112</v>
+        <v>0.0018935731548933574</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.022438201353649673</v>
       </c>
       <c r="B36">
-        <v>0.0015335011467174746</v>
+        <v>0.001637609656921382</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.023079292820896807</v>
       </c>
       <c r="B37">
-        <v>0.0012743164136829359</v>
+        <v>0.0013626331742109009</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.02372038428814394</v>
       </c>
       <c r="B38">
-        <v>0.000995542117073086</v>
+        <v>0.0010666463570425551</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.024361475755391073</v>
       </c>
       <c r="B39">
-        <v>0.000693242458038099</v>
+        <v>0.000744683637370009</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.02500256722263821</v>
       </c>
       <c r="B40">
-        <v>0.00036290067340479621</v>
+        <v>0.00039103739256518316</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.02564365868988534</v>
       </c>
       <c r="B41">
-        <v>-8.89693134785615E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.02500256722263821</v>
       </c>
       <c r="B43">
-        <v>0.00016594363928208841</v>
+        <v>0.00013780692012170152</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.024361475755391073</v>
       </c>
       <c r="B44">
-        <v>0.00033315420271472977</v>
+        <v>0.00028171302338281983</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.02372038428814394</v>
       </c>
       <c r="B45">
-        <v>0.0004978124372868011</v>
+        <v>0.00042670819731733194</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.023079292820896807</v>
       </c>
       <c r="B46">
-        <v>0.00065609908998718008</v>
+        <v>0.00056778232945921508</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.022438201353649673</v>
       </c>
       <c r="B47">
-        <v>0.00080474157529012184</v>
+        <v>0.00070063306508621461</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.02179710988640254</v>
       </c>
       <c r="B48">
-        <v>0.00094265397761139115</v>
+        <v>0.00082378908045114554</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.021156018419155407</v>
       </c>
       <c r="B49">
-        <v>0.0010692970488521316</v>
+        <v>0.00093648680955059273</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.020514926951908274</v>
       </c>
       <c r="B50">
-        <v>0.0011841315409134854</v>
+        <v>0.0010379626863811389</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.019873835484661137</v>
       </c>
       <c r="B51">
-        <v>0.0012868332462369421</v>
+        <v>0.0011277338492733746</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.019232744017414004</v>
       </c>
       <c r="B52">
-        <v>0.0013779381194253806</v>
+        <v>0.0012064402538939187</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.018591652550166874</v>
       </c>
       <c r="B53">
-        <v>0.001458197155622027</v>
+        <v>0.0012750025602433969</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.017950561082919741</v>
       </c>
       <c r="B54">
-        <v>0.001528361349970108</v>
+        <v>0.0013343414283224359</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.017309469615672604</v>
       </c>
       <c r="B55">
-        <v>0.0015890279117925744</v>
+        <v>0.0013851830390300361</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.016668378148425471</v>
       </c>
       <c r="B56">
-        <v>0.0016401789071312765</v>
+        <v>0.0014274756568587016</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.016027286681178338</v>
       </c>
       <c r="B57">
-        <v>0.0016816426162077891</v>
+        <v>0.0014609730671993121</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.015386195213931206</v>
       </c>
       <c r="B58">
-        <v>0.0017132473192436879</v>
+        <v>0.0014854290554427465</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.014745103746684071</v>
       </c>
       <c r="B59">
-        <v>0.0017348426772761977</v>
+        <v>0.001500627747050525</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.014104012279436938</v>
       </c>
       <c r="B60">
-        <v>0.0017463638746051423</v>
+        <v>0.0015064746277667297</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.013462920812189803</v>
       </c>
       <c r="B61">
-        <v>0.0017477674763459966</v>
+        <v>0.0015029055234060834</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.01282182934494267</v>
       </c>
       <c r="B62">
-        <v>0.0017390100476142344</v>
+        <v>0.0014898562597833087</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.012180737877695537</v>
       </c>
       <c r="B63">
-        <v>0.0017202291200586189</v>
+        <v>0.0014674981700965155</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.011539646410448403</v>
       </c>
       <c r="B64">
-        <v>0.0016922860914610686</v>
+        <v>0.0014369446170773607</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.01089855494320127</v>
       </c>
       <c r="B65">
-        <v>0.0016562233261367917</v>
+        <v>0.0013995444708408884</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.010257463475954137</v>
       </c>
       <c r="B66">
-        <v>0.0016130831884009957</v>
+        <v>0.0013566466015021424</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.0096163720087070019</v>
       </c>
       <c r="B67">
-        <v>0.001562514204895838</v>
+        <v>0.0013078101515520068</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.00897528054145987</v>
       </c>
       <c r="B68">
-        <v>0.0014985895515712748</v>
+        <v>0.0012454353529847268</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0083341890742127354</v>
       </c>
       <c r="B69">
-        <v>0.0014166906095304554</v>
+        <v>0.0011636079090419247</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0076930976069656031</v>
       </c>
       <c r="B70">
-        <v>0.001323006931181507</v>
+        <v>0.001070314318451377</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.007052006139718469</v>
       </c>
       <c r="B71">
-        <v>0.0012242857852744302</v>
+        <v>0.00097426102522278483</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0064109146724713349</v>
       </c>
       <c r="B72">
-        <v>0.0011186971346217461</v>
+        <v>0.00087313345900740435</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0057698232052242017</v>
       </c>
       <c r="B73">
-        <v>0.0010032606328155673</v>
+        <v>0.00076314160793725951</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0051287317379770684</v>
       </c>
       <c r="B74">
-        <v>0.00087897200250384977</v>
+        <v>0.00064561470842589323</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0044876402707299352</v>
       </c>
       <c r="B75">
-        <v>0.00074783584831898968</v>
+        <v>0.00052318293838976094</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0038465488034828015</v>
       </c>
       <c r="B76">
-        <v>0.00061191623377529361</v>
+        <v>0.00039856099347544769</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0032054573362356674</v>
       </c>
       <c r="B77">
-        <v>0.00047309310424649626</v>
+        <v>0.0002742312988332832</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0025643658689885342</v>
       </c>
       <c r="B78">
-        <v>0.00033245047366213738</v>
+        <v>0.00015166267989844589</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0019232744017414008</v>
       </c>
       <c r="B79">
-        <v>0.00019200309974613605</v>
+        <v>3.3525289042644781E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0012821829344942671</v>
       </c>
       <c r="B80">
-        <v>5.5459022761962229E-05</v>
+        <v>-7.5323636556452918E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00064109146724713355</v>
       </c>
       <c r="B81">
-        <v>-6.7652825479122769E-05</v>
+        <v>-0.00016253436263169845</v>
       </c>
     </row>
     <row r="82" spans="1:2">
